--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -775,13 +775,13 @@
         <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>176.45</v>
+        <v>187.87</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>243.12</v>
+        <v>254.54</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -5008,45 +5008,46 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>07:15 AM</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>06:40 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Awaiting Checkout)</t>
-        </is>
-      </c>
-    </row>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -775,13 +775,13 @@
         <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>187.87</v>
+        <v>200.04</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>254.54</v>
+        <v>266.71</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5047,15 +5047,58 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>07:30 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="14" t="n"/>
+      <c r="F33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F33" s="15">
-        <f>SUM(F2:F31)</f>
+      <c r="F34" s="15">
+        <f>SUM(F2:F32)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -775,13 +775,13 @@
         <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>200.04</v>
+        <v>207.64</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>266.71</v>
+        <v>274.31</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5087,18 +5087,58 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="14" t="n"/>
-      <c r="F33" s="15" t="n"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>07:24 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>7h 36m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="14" t="n"/>
+      <c r="F34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F34" s="15">
-        <f>SUM(F2:F32)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -775,10 +775,10 @@
         <v>66.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>207.64</v>
+        <v>208.31</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>274.31</v>
+        <v>274.98</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>30</v>
@@ -5105,16 +5105,16 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>7h 36m</t>
+          <t>8h 16m</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7.6</v>
+        <v>8.27</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
         </is>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -613,13 +613,13 @@
         <v>85.16</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>178.17</v>
+        <v>209.84</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>263.3299999999999</v>
+        <v>295</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10079,14 +10079,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>9h 40m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 05:40 PM / 9h 40m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -586,13 +586,13 @@
         <v>77</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>196.17</v>
+        <v>206.67</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>273.17</v>
+        <v>283.67</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -667,13 +667,13 @@
         <v>74.75</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>173.6</v>
+        <v>198.86</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>248.35</v>
+        <v>273.61</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         <v>72</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7605,14 +7605,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>
@@ -10221,7 +10341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11436,14 +11556,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:30 AM – 06:00 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (10:00 AM – 06:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>11h 30m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (06:30 AM – 06:00 PM / 11h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>
@@ -12695,7 +12935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13910,14 +14150,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>05:30 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 05:30 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -640,13 +640,13 @@
         <v>75.08</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>177</v>
+        <v>204.17</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>252.08</v>
+        <v>279.25</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6368,14 +6368,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -748,13 +748,13 @@
         <v>71</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>172.68</v>
+        <v>191.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>243.68</v>
+        <v>262.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9082,14 +9082,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>10h 30m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -613,10 +613,10 @@
         <v>85.16</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>209.84</v>
+        <v>210.5</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>295</v>
+        <v>295.66</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>31</v>
@@ -10537,28 +10537,29 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>06:20 PM</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>9h 40m</t>
+          <t>10h 20m</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>9.67</v>
+        <v>10.33</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 05:40 PM / 9h 40m)</t>
-        </is>
-      </c>
-    </row>
+          <t>⚡ Live Extended Station Duty (08:00 AM – 06:20 PM / 10h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -694,13 +694,13 @@
         <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>175.25</v>
+        <v>204.09</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>247.25</v>
+        <v>276.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2096,14 +2096,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8h 10m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>12h 15m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (03:30 AM – 03:45 PM / 12h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F35" s="15">
+        <f>SUM(F2:F33)</f>
         <v/>
       </c>
     </row>
@@ -10559,7 +10679,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -802,13 +802,13 @@
         <v>69.33</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>169.67</v>
+        <v>189.67</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13273,14 +13273,174 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11h 00m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 06:00 PM / 11h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F32" s="15">
-        <f>SUM(F2:F30)</f>
+      <c r="F36" s="15">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -17,8 +17,6 @@
     <sheet name="Raboushee" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Rasheed Akel" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Yasmin" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Talal" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tarek Orfhly" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,12 +75,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -138,19 +130,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -524,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -533,7 +516,6 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -567,11 +549,6 @@
           <t>Active Days Logged</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -579,25 +556,20 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Rasheed Akel</t>
+          <t>Mohammad Almohammad</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>77</v>
+        <v>85.16</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>206.67</v>
+        <v>210.5</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>283.67</v>
+        <v>295.66</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -606,25 +578,20 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Mohammad Almohammad</t>
+          <t>Rasheed Akel</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>85.16</v>
+        <v>77</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>210.5</v>
+        <v>206.67</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>295.66</v>
+        <v>283.67</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -648,11 +615,6 @@
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -660,25 +622,20 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Joudi Alghorani</t>
+          <t>Osama Alkabbani</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.75</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>198.86</v>
+        <v>205</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>273.61</v>
+        <v>277</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -702,11 +659,6 @@
       <c r="F6" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -714,25 +666,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Osama Alkabbani</t>
+          <t>Omar Elnemr</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>72</v>
+        <v>66.67</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>205</v>
+        <v>208.31</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>277</v>
+        <v>274.98</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -741,25 +688,20 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Khaled</t>
+          <t>Joudi Alghorani</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>71</v>
+        <v>74.75</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>191.6</v>
+        <v>198.86</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>262.6</v>
+        <v>273.61</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+        <v>31</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -768,25 +710,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Omar Elnemr</t>
+          <t>Khaled</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>66.67</v>
+        <v>71</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>208.31</v>
+        <v>191.6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>274.98</v>
+        <v>262.6</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>30</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -809,65 +746,6 @@
       </c>
       <c r="F10" s="2" t="n">
         <v>29</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Tarek Orfhly</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Talal</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +1880,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -2010,7 +1888,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -2217,1687 +2095,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Log-In</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Log-Out</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Decimal Hours</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Off / Not scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Off / Not scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Off / Not scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Morning flight shift (9h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>03:00 AM</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13h 00m</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Morning flight shift (4:00 PM return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>03:00 AM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13h 00m</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Total Logged Hours</t>
-        </is>
-      </c>
-      <c r="F22" s="15">
-        <f>SUM(F2:F20)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Log-In</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Log-Out</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Decimal Hours</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>06:30 AM</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Standardized</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>8h 30m</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Standard daytime shift</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled weekly day off</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Morning flight shift (9h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Morning flight shift (4:00 PM return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Morning flight shift (4:00 PM return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Morning flight shift (4:00 PM return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Total Logged Hours</t>
-        </is>
-      </c>
-      <c r="F22" s="15">
-        <f>SUM(F2:F20)</f>
         <v/>
       </c>
     </row>
@@ -4713,7 +2917,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -4721,7 +2925,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
@@ -4993,7 +3197,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -5001,7 +3205,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -5247,17 +3451,13 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="n"/>
-      <c r="F34" s="15" t="n"/>
-    </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -5994,7 +4194,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -6002,7 +4202,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -6394,7 +4594,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -6402,7 +4602,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -6609,12 +4809,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -7711,7 +5911,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -7719,7 +5919,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -7966,12 +6166,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -9068,7 +7268,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -9076,7 +7276,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -9228,7 +7428,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -9236,7 +7436,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -9323,12 +7523,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -10505,7 +8705,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -10513,7 +8713,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -10680,12 +8880,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -11502,7 +9702,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -11510,7 +9710,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
@@ -11822,7 +10022,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -11830,7 +10030,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>🌴 Contractual Paid Rest Day (Off Duty)</t>
         </is>
@@ -12037,12 +10237,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>
@@ -12859,7 +11059,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -12867,7 +11067,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -13139,7 +11339,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -13147,7 +11347,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -13379,7 +11579,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -13387,7 +11587,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -13419,7 +11619,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -13427,19 +11627,19 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="12">
         <f>SUM(F2:F34)</f>
         <v/>
       </c>
@@ -14736,7 +12936,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -14744,7 +12944,7 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -14776,7 +12976,7 @@
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -14784,19 +12984,19 @@
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="12">
         <f>SUM(F2:F33)</f>
         <v/>
       </c>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -141,6 +147,15 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2116,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3451,14 +3466,58 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>08:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -688,13 +688,13 @@
         <v>66.67</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>208.31</v>
+        <v>215.48</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>274.98</v>
+        <v>282.15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -3467,42 +3467,42 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>08:00 PM</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>03:10 AM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7h 10m</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Night Shift</t>
         </is>
       </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Awaiting Checkout)</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
         </is>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -600,13 +600,13 @@
         <v>77</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>206.67</v>
+        <v>219</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>283.67</v>
+        <v>296</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -11714,7 +11714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13049,14 +13049,58 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>07:20 PM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>12h 20m</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -578,13 +578,13 @@
         <v>85.16</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>210.5</v>
+        <v>222.83</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>295.66</v>
+        <v>307.99</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8938,14 +8938,58 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>07:20 PM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>12h 20m</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:20 PM / 12h 20m)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -578,13 +578,13 @@
         <v>85.16</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>222.83</v>
+        <v>234.93</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>307.99</v>
+        <v>320.09</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -7603,7 +7603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8978,18 +8978,58 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>07:06 PM</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>12h 06m</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (07:00 AM – 07:06 PM / 12h 06m)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F37" s="12">
+        <f>SUM(F2:F35)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -644,13 +644,13 @@
         <v>72</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>205</v>
+        <v>218.5</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>277</v>
+        <v>290.5</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -9044,7 +9044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10379,14 +10379,58 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>05:30 AM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>13h 30m</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Extended Shift</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>⚡ Live Extended Station Duty (05:30 AM – 07:00 PM / 13h 30m)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -666,13 +666,13 @@
         <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>204.09</v>
+        <v>213.09</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>276.09</v>
+        <v>285.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -688,13 +688,13 @@
         <v>66.67</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>215.48</v>
+        <v>224.48</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>282.15</v>
+        <v>291.15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -732,13 +732,13 @@
         <v>71</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>191.6</v>
+        <v>200.6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>262.6</v>
+        <v>271.6</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -754,13 +754,13 @@
         <v>69.33</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>189.67</v>
+        <v>198.17</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>259</v>
+        <v>267.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -769,1363 +769,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Log-In</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Log-Out</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Decimal Hours</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>07:45 AM</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7h 15m</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (07:45 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>7h 00m</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (08:00 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>07:30 AM</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8h 30m</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>04:00 AM</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12h 00m</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (12h 00m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>6h 00m</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6h 00m</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>6h 00m</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>09:00 AM</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>03:00 PM</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6h 00m</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Training / Paid</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>03:30 AM</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>13h 00m</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>04:00 AM</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>12h 30m</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Ground Duty (08:00 AM – 05:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>07:15 AM</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>03:40 PM</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>8h 25m</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>07:30 AM</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>03:40 PM</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>8h 10m</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:40 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>03:30 AM</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>03:45 PM</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>12h 15m</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (03:30 AM – 03:45 PM / 12h 15m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Total Logged Hours</t>
-        </is>
-      </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2199,7 +842,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>06:30 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2209,20 +852,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Standardized</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2239,7 +882,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -2249,11 +892,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -2262,7 +905,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2279,30 +922,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>05:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9h 25m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9.42</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>⚡ Extended shift (+1h 40m overtime)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2319,7 +962,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2329,11 +972,11 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -2342,7 +985,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2359,7 +1002,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2369,11 +1012,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2382,7 +1025,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift (4:00 PM return)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2399,7 +1042,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2409,11 +1052,11 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -2422,7 +1065,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (4:00 PM return)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2439,7 +1082,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>08:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2449,11 +1092,11 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2462,45 +1105,45 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift (4:00 PM return)</t>
+          <t>Standard morning bus shift (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -2519,108 +1162,108 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7h 15m</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Training Session (07:45 AM – 03:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F12" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -2639,30 +1282,30 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>7h 00m</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Paid Standby</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+          <t>🎓 Training Session (08:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2679,30 +1322,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.33</v>
+        <v>8.5</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2719,30 +1362,30 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>04:45 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>9h 25m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>9.42</v>
+        <v>9</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2759,7 +1402,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2769,20 +1412,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8h 45m</t>
+          <t>12h 00m</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.75</v>
+        <v>12</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 00m)</t>
         </is>
       </c>
     </row>
@@ -2799,7 +1442,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>07:10 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -2809,11 +1452,11 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>8h 50m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
@@ -2822,7 +1465,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 04:00 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2839,21 +1482,21 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>07:10 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>05:53 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10h 43m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.72</v>
+        <v>9</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -2862,7 +1505,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 05:53 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2879,21 +1522,21 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>07:07 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>9h 08m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>9.130000000000001</v>
+        <v>9</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
@@ -2902,7 +1545,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:07 AM / Logged out 04:15 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2919,30 +1562,30 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -2959,21 +1602,21 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>05:45 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>10h 30m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -2982,7 +1625,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 05:45 PM)</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -2999,21 +1642,21 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>05:10 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9h 50m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.83</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3022,7 +1665,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 05:10 PM)</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3039,21 +1682,21 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>9.33</v>
+        <v>6</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -3062,7 +1705,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 04:40 PM)</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3079,21 +1722,21 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>09:00 AM</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>03:00 PM</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9h 25m</t>
+          <t>6h 00m</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9.42</v>
+        <v>6</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3102,7 +1745,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 04:40 PM)</t>
+          <t>🎓 Training Session (09:00 AM – 03:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3119,30 +1762,30 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>01:10 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>5h 55m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>5.92</v>
+        <v>9.5</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 01:10 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -3159,21 +1802,21 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>04:17 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8h 57m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.949999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -3182,87 +1825,87 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:20 AM / Logged out 04:17 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 04:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>13h 00m</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (13h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>07:15 AM</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8h 45m</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3279,30 +1922,30 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>04:00 AM</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>07:04 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>11h 49m</t>
+          <t>12h 30m</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>11.82</v>
+        <v>12.5</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 07:04 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
         </is>
       </c>
     </row>
@@ -3319,7 +1962,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>07:15 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3329,11 +1972,11 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9h 45m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -3342,7 +1985,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 05:00 PM)</t>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 05:00 PM)</t>
         </is>
       </c>
     </row>
@@ -3364,16 +2007,16 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>06:40 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>11h 25m</t>
+          <t>8h 25m</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>11.42</v>
+        <v>8.42</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -3382,7 +2025,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
         </is>
       </c>
     </row>
@@ -3399,21 +2042,21 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>07:30 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12h 10m</t>
+          <t>8h 10m</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>12.17</v>
+        <v>8.17</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -3422,7 +2065,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:40 PM)</t>
         </is>
       </c>
     </row>
@@ -3439,70 +2082,70 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>07:24 AM</t>
+          <t>03:30 AM</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>03:40 PM</t>
+          <t>03:45 PM</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>8h 16m</t>
+          <t>12h 15m</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>8.27</v>
+        <v>12.25</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
+          <t>✈️ Early dawn flight departure handling (03:30 AM – 03:45 PM / 12h 15m)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>08:00 PM</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>03:10 AM</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>7h 10m</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Night Shift</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
         </is>
       </c>
     </row>
@@ -3526,13 +2169,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3640,7 +2283,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -3650,11 +2293,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>7h 50m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7.83</v>
+        <v>7.75</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -3663,7 +2306,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 50m)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
@@ -3685,25 +2328,25 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>05:40 PM</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7h 45m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7.75</v>
+        <v>9.42</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift (7h 45m)</t>
+          <t>⚡ Extended shift (+1h 40m overtime)</t>
         </is>
       </c>
     </row>
@@ -3720,30 +2363,30 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>13h 00m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>13</v>
+        <v>7.75</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight check-in &amp; departure (13.0 hrs)</t>
+          <t>Standard daytime shift</t>
         </is>
       </c>
     </row>
@@ -3760,21 +2403,21 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -3783,7 +2426,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:30 PM return)</t>
+          <t>Standard daytime shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -3800,21 +2443,21 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -3823,7 +2466,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:30 PM return)</t>
+          <t>Standard daytime shift (4:00 PM return)</t>
         </is>
       </c>
     </row>
@@ -3840,228 +2483,228 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Standard daytime shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Morning departure processing (4:00 PM return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F12" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -4080,21 +2723,21 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -4120,21 +2763,21 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:45 PM</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8.08</v>
+        <v>9.42</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -4160,7 +2803,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>03:30 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4170,20 +2813,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12h 30m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>12.5</v>
+        <v>8.75</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4200,7 +2843,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>03:20 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -4210,60 +2853,60 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>12h 40m</t>
+          <t>8h 50m</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>12.67</v>
+        <v>8.83</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (12h 40m)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>07:10 AM</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>05:53 PM</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10h 43m</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 05:53 PM)</t>
         </is>
       </c>
     </row>
@@ -4280,70 +2923,70 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>12h 45m</t>
+          <t>9h 08m</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>12.75</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (12h 45m)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:07 AM / Logged out 04:15 PM)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9h 00m</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Paid Standby</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
@@ -4360,21 +3003,21 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:45 PM</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -4383,7 +3026,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 05:45 PM)</t>
         </is>
       </c>
     </row>
@@ -4400,21 +3043,21 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>05:10 PM</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 50m</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8</v>
+        <v>9.83</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -4423,7 +3066,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 05:10 PM)</t>
         </is>
       </c>
     </row>
@@ -4440,21 +3083,21 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>04:15 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>8.25</v>
+        <v>9.33</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -4463,7 +3106,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -4480,21 +3123,21 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8</v>
+        <v>9.42</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -4503,7 +3146,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -4520,21 +3163,21 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>01:30 PM</t>
+          <t>01:10 PM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>5h 30m</t>
+          <t>5h 55m</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>5.5</v>
+        <v>5.92</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -4543,7 +3186,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 01:10 PM)</t>
         </is>
       </c>
     </row>
@@ -4560,21 +3203,21 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:17 PM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>8h 57m</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -4583,87 +3226,87 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
+          <t>✈️ Live Daily Duty (Logged in 07:20 AM / Logged out 04:17 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>03:30 PM</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>8h 30m</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>0h 00m</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Day Off</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4680,30 +3323,30 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>07:04 PM</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>11h 49m</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>13.25</v>
+        <v>11.82</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Dawn Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 07:04 PM)</t>
         </is>
       </c>
     </row>
@@ -4720,7 +3363,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4730,11 +3373,11 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 45m</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -4743,7 +3386,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty</t>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 05:00 PM)</t>
         </is>
       </c>
     </row>
@@ -4765,16 +3408,16 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>03:40 PM</t>
+          <t>06:40 PM</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>8h 25m</t>
+          <t>11h 25m</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>8.42</v>
+        <v>11.42</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -4783,7 +3426,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
         </is>
       </c>
     </row>
@@ -4800,30 +3443,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:30 PM</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10h 30m</t>
+          <t>12h 10m</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.5</v>
+        <v>12.17</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Extended Shift</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
         </is>
       </c>
     </row>
@@ -4840,21 +3483,21 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>07:24 AM</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>03:45 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>8h 16m</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -4863,18 +3506,102 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:45 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>08:00 PM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>03:10 AM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7h 10m</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F37" s="12">
+        <f>SUM(F2:F35)</f>
         <v/>
       </c>
     </row>
@@ -4883,13 +3610,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4997,7 +3724,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:10 AM</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -5007,11 +3734,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>7h 50m</t>
         </is>
       </c>
       <c r="F3" s="7" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -5020,7 +3747,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (7h 50m)</t>
         </is>
       </c>
     </row>
@@ -5037,7 +3764,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:15 AM</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -5047,11 +3774,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>7h 45m</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -5060,7 +3787,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Standard daytime shift</t>
+          <t>Standard daytime shift (7h 45m)</t>
         </is>
       </c>
     </row>
@@ -5077,7 +3804,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>03:15 AM</t>
+          <t>03:30 AM</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -5087,11 +3814,11 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>13h 15m</t>
+          <t>13h 00m</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -5100,7 +3827,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>✈️ Early dawn flight check-in &amp; boarding (13h 15m)</t>
+          <t>✈️ Early dawn flight check-in &amp; departure (13.0 hrs)</t>
         </is>
       </c>
     </row>
@@ -5122,16 +3849,16 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -5140,7 +3867,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Morning departure processing (4:00 PM return)</t>
+          <t>Morning departure processing (4:30 PM return)</t>
         </is>
       </c>
     </row>
@@ -5162,16 +3889,16 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>9h 00m</t>
+          <t>9h 30m</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -5180,7 +3907,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Morning departure processing</t>
+          <t>Morning departure processing (4:30 PM return)</t>
         </is>
       </c>
     </row>
@@ -5220,205 +3947,205 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Morning departure processing</t>
+          <t>Morning departure processing (4:00 PM return)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -5442,16 +4169,16 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -5482,16 +4209,16 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>04:05 PM</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>8h 05m</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8.5</v>
+        <v>8.08</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -5517,7 +4244,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>03:30 AM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -5527,20 +4254,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>12h 30m</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 30m)</t>
         </is>
       </c>
     </row>
@@ -5557,7 +4284,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>03:20 AM</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -5567,60 +4294,60 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>12h 40m</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>8</v>
+        <v>12.67</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
+          <t>✈️ Early dawn flight departure handling (12h 40m)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>03:15 AM</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12h 45m</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Dawn Shift</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Early dawn flight departure handling (12h 45m)</t>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
@@ -5637,68 +4364,68 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>12h 45m</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (12h 45m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F20" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>04:30 PM</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9h 30m</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -5717,21 +4444,21 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>08:20 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>7h 40m</t>
+          <t>8h 30m</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7.67</v>
+        <v>8.5</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -5757,7 +4484,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>08:05 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5767,11 +4494,11 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7h 55m</t>
+          <t>8h 00m</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -5802,16 +4529,16 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
@@ -5877,21 +4604,21 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>08:10 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>01:30 PM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>4h 50m</t>
+          <t>5h 30m</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4.83</v>
+        <v>5.5</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -5940,87 +4667,87 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+          <t>✈️ Live Morning Airport Ground Duty</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>07:15 AM</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8h 45m</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Official Duty</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
         </is>
       </c>
     </row>
@@ -6037,30 +4764,30 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>03:15 AM</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>04:40 PM</t>
+          <t>04:30 PM</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>9h 20m</t>
+          <t>13h 15m</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>9.33</v>
+        <v>13.25</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Dawn Shift</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+          <t>✈️ Early dawn flight departure handling (13h 15m)</t>
         </is>
       </c>
     </row>
@@ -6077,21 +4804,21 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>07:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>04:51 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9h 21m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.35</v>
+        <v>9</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -6100,7 +4827,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+          <t>✈️ Live Daily Ground Duty</t>
         </is>
       </c>
     </row>
@@ -6157,30 +4884,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>03:45 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8h 25m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.42</v>
+        <v>10.5</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Extended Shift</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+          <t>⚡ Live Extended Station Duty (07:30 AM – 06:00 PM / 10h 30m)</t>
         </is>
       </c>
     </row>
@@ -6197,7 +4924,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>07:20 AM</t>
+          <t>07:30 AM</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -6207,11 +4934,11 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>8h 25m</t>
+          <t>8h 15m</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>8.42</v>
+        <v>8.25</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -6220,18 +4947,62 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+          <t>✈️ Live Morning Airport Ground Duty (07:30 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>
@@ -6240,13 +5011,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6359,6 +5130,1407 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Standard daytime shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Standard daytime shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>13h 15m</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight check-in &amp; boarding (13h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Morning departure processing (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Morning departure processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Morning departure processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (08:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12h 45m</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Early dawn flight departure handling (12h 45m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>08:20 AM</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>7h 40m</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>08:05 AM</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7h 55m</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>08:10 AM</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>4h 50m</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 00m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (8h 45m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>04:40 PM</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>9h 20m</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (9h 20m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>07:30 AM</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>04:51 PM</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>9h 21m</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (9h 21m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:15 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:20 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Total Logged Hours</t>
+        </is>
+      </c>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Log-In</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Log-Out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Decimal Hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Standardized</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
           <t>04:30 PM</t>
         </is>
       </c>
@@ -6582,40 +6754,40 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -7581,14 +7753,58 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F35" s="12">
-        <f>SUM(F2:F33)</f>
+      <c r="F36" s="12">
+        <f>SUM(F2:F34)</f>
         <v/>
       </c>
     </row>
@@ -10445,7 +10661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11820,14 +12036,58 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 04:30 PM)</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F37" s="12">
+        <f>SUM(F2:F35)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -688,13 +688,13 @@
         <v>66.67</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>224.48</v>
+        <v>231.73</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>291.15</v>
+        <v>298.4</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -2175,7 +2175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2511,200 +2511,200 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -3590,18 +3590,94 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="F36" s="12" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>08:20 AM</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>7h 15m</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 08:20 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F37" s="12">
-        <f>SUM(F2:F35)</f>
+      <c r="F39" s="12">
+        <f>SUM(F2:F37)</f>
         <v/>
       </c>
     </row>

--- a/attendance_team_individual_tabs_2026.xlsx
+++ b/attendance_team_individual_tabs_2026.xlsx
@@ -622,13 +622,13 @@
         <v>75.08</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>204.17</v>
+        <v>211.84</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>279.25</v>
+        <v>286.92</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -666,13 +666,13 @@
         <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>213.09</v>
+        <v>229.59</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>285.09</v>
+        <v>301.59</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -710,13 +710,13 @@
         <v>74.75</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>198.86</v>
+        <v>215.28</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>273.61</v>
+        <v>290.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -732,13 +732,13 @@
         <v>71</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>200.6</v>
+        <v>209.27</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>271.6</v>
+        <v>280.27</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -754,13 +754,13 @@
         <v>69.33</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>198.17</v>
+        <v>207.17</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>267.5</v>
+        <v>276.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1110,40 +1110,40 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -1190,80 +1190,80 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -1550,40 +1550,40 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -2149,18 +2149,94 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8h 45m</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F38" s="12">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
     </row>
@@ -3692,7 +3768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4028,200 +4104,200 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -4468,40 +4544,40 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -5067,18 +5143,94 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>7h 40m</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F38" s="12">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
     </row>
@@ -5093,7 +5245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5429,200 +5581,200 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>04:30 PM</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>9h 30m</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="7" t="n">
         <v>9.5</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -5869,40 +6021,40 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>04:30 PM</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>9h 30m</t>
         </is>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -6468,18 +6620,94 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (08:00 AM – 03:45 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8h 40m</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F38" s="12">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
     </row>
@@ -6494,7 +6722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6830,40 +7058,40 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>04:00 PM</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -7869,18 +8097,94 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03:40 PM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8h 40m</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (07:00 AM – 03:40 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F36" s="12">
-        <f>SUM(F2:F34)</f>
+      <c r="F38" s="12">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
     </row>
@@ -10737,7 +11041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12152,18 +12456,58 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="F36" s="12" t="n"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (07:00 AM – 04:00 PM)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="11" t="n"/>
+      <c r="F37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Total Logged Hours</t>
         </is>
       </c>
-      <c r="F37" s="12">
-        <f>SUM(F2:F35)</f>
+      <c r="F38" s="12">
+        <f>SUM(F2:F36)</f>
         <v/>
       </c>
     </row>
